--- a/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -377,7 +377,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -681,7 +681,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -764,7 +764,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -855,7 +855,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -878,7 +878,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1080,7 +1080,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1139,7 +1139,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1172,7 +1172,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1184,7 +1184,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1298,7 +1298,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1378,7 +1378,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1415,7 +1415,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1550,7 +1550,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2145,7 +2145,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -9263,7 +9263,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>492</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>507</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>520</v>
       </c>
@@ -12887,7 +12887,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>533</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>547</v>
       </c>
@@ -15305,12 +15305,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP109">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="562">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1310,6 +1310,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -7198,7 +7202,7 @@
         <v>411</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>103</v>
+        <v>412</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -7207,10 +7211,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7221,10 +7225,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7250,10 +7254,10 @@
         <v>408</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7304,7 +7308,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7316,7 +7320,7 @@
         <v>411</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>103</v>
+        <v>412</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
@@ -7325,10 +7329,10 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -7339,10 +7343,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7368,16 +7372,16 @@
         <v>233</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7406,7 +7410,7 @@
       </c>
       <c r="Y44" s="2"/>
       <c r="Z44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -7424,7 +7428,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7442,10 +7446,10 @@
         <v>80</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>341</v>
@@ -7459,10 +7463,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7488,16 +7492,16 @@
         <v>233</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7525,10 +7529,10 @@
         <v>355</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7546,7 +7550,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7564,10 +7568,10 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>341</v>
@@ -7581,10 +7585,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7607,17 +7611,17 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7666,7 +7670,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7690,7 +7694,7 @@
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
@@ -7701,10 +7705,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7730,10 +7734,10 @@
         <v>153</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7784,7 +7788,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7805,10 +7809,10 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
@@ -7819,10 +7823,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7845,16 +7849,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7904,7 +7908,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7925,10 +7929,10 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>80</v>
@@ -7939,10 +7943,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7965,16 +7969,16 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8024,7 +8028,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8045,10 +8049,10 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
@@ -8059,10 +8063,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8088,16 +8092,16 @@
         <v>390</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8134,10 +8138,10 @@
         <v>80</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>80</v>
@@ -8146,7 +8150,7 @@
         <v>141</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8167,10 +8171,10 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -8181,10 +8185,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8299,10 +8303,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8415,13 +8419,13 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="B53" t="s" s="2">
-        <v>466</v>
-      </c>
       <c r="C53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>80</v>
@@ -8443,13 +8447,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8535,10 +8539,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8657,10 +8661,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8686,13 +8690,13 @@
         <v>233</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>247</v>
@@ -8742,7 +8746,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8760,7 +8764,7 @@
         <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>252</v>
@@ -8777,10 +8781,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8806,13 +8810,13 @@
         <v>312</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M56" t="s" s="2">
         <v>314</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>316</v>
@@ -8864,7 +8868,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8882,7 +8886,7 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>319</v>
@@ -8899,10 +8903,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8928,13 +8932,13 @@
         <v>233</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>326</v>
@@ -8965,10 +8969,10 @@
         <v>336</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -8986,7 +8990,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9021,10 +9025,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9108,7 +9112,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9143,10 +9147,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9172,10 +9176,10 @@
         <v>81</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>393</v>
@@ -9230,7 +9234,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9265,13 +9269,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>80</v>
@@ -9296,16 +9300,16 @@
         <v>390</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9354,7 +9358,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9375,10 +9379,10 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9389,10 +9393,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9507,10 +9511,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9623,13 +9627,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>80</v>
@@ -9651,13 +9655,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9743,10 +9747,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9865,10 +9869,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9894,13 +9898,13 @@
         <v>233</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>247</v>
@@ -9910,7 +9914,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>80</v>
@@ -9950,7 +9954,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>91</v>
@@ -9968,7 +9972,7 @@
         <v>80</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>252</v>
@@ -9985,10 +9989,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10011,16 +10015,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>314</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>316</v>
@@ -10033,7 +10037,7 @@
         <v>80</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>80</v>
@@ -10072,7 +10076,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10090,7 +10094,7 @@
         <v>80</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>319</v>
@@ -10107,10 +10111,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10136,13 +10140,13 @@
         <v>233</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>326</v>
@@ -10173,10 +10177,10 @@
         <v>336</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>80</v>
@@ -10194,7 +10198,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10229,10 +10233,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10316,7 +10320,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10351,10 +10355,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10380,10 +10384,10 @@
         <v>81</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>393</v>
@@ -10438,7 +10442,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10473,13 +10477,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>80</v>
@@ -10504,16 +10508,16 @@
         <v>390</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10562,7 +10566,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10583,10 +10587,10 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10597,10 +10601,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10715,10 +10719,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10831,13 +10835,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>80</v>
@@ -10859,13 +10863,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10951,10 +10955,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11073,10 +11077,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11102,13 +11106,13 @@
         <v>233</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O75" t="s" s="2">
         <v>247</v>
@@ -11118,7 +11122,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>80</v>
@@ -11158,7 +11162,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>91</v>
@@ -11176,7 +11180,7 @@
         <v>80</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>252</v>
@@ -11193,10 +11197,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11219,16 +11223,16 @@
         <v>92</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
         <v>314</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>316</v>
@@ -11241,7 +11245,7 @@
         <v>80</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>80</v>
@@ -11280,7 +11284,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11298,7 +11302,7 @@
         <v>80</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>319</v>
@@ -11315,10 +11319,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11344,13 +11348,13 @@
         <v>233</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>326</v>
@@ -11381,10 +11385,10 @@
         <v>336</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11402,7 +11406,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11437,10 +11441,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11524,7 +11528,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11559,10 +11563,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11588,10 +11592,10 @@
         <v>81</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>393</v>
@@ -11646,7 +11650,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11681,13 +11685,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D80" t="s" s="2">
         <v>80</v>
@@ -11712,16 +11716,16 @@
         <v>390</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -11770,7 +11774,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11791,10 +11795,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -11805,10 +11809,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11923,10 +11927,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12039,13 +12043,13 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>80</v>
@@ -12067,13 +12071,13 @@
         <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12159,10 +12163,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12281,10 +12285,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12310,13 +12314,13 @@
         <v>233</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>247</v>
@@ -12326,7 +12330,7 @@
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>80</v>
@@ -12366,7 +12370,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>91</v>
@@ -12384,7 +12388,7 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>252</v>
@@ -12401,10 +12405,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12427,16 +12431,16 @@
         <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M86" t="s" s="2">
         <v>314</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>316</v>
@@ -12449,7 +12453,7 @@
         <v>80</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>80</v>
@@ -12488,7 +12492,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12506,7 +12510,7 @@
         <v>80</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>319</v>
@@ -12523,10 +12527,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12552,13 +12556,13 @@
         <v>233</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>326</v>
@@ -12589,10 +12593,10 @@
         <v>336</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>80</v>
@@ -12610,7 +12614,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12645,10 +12649,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12732,7 +12736,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12767,10 +12771,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12796,10 +12800,10 @@
         <v>81</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>393</v>
@@ -12854,7 +12858,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12889,13 +12893,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>80</v>
@@ -12920,16 +12924,16 @@
         <v>390</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
@@ -12978,7 +12982,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12999,10 +13003,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13013,10 +13017,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13131,10 +13135,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13247,13 +13251,13 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D93" t="s" s="2">
         <v>80</v>
@@ -13275,13 +13279,13 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13367,10 +13371,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13489,10 +13493,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13518,13 +13522,13 @@
         <v>233</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>247</v>
@@ -13534,7 +13538,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>80</v>
@@ -13574,7 +13578,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13592,7 +13596,7 @@
         <v>80</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>252</v>
@@ -13609,10 +13613,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13635,16 +13639,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M96" t="s" s="2">
         <v>314</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O96" t="s" s="2">
         <v>316</v>
@@ -13657,7 +13661,7 @@
         <v>80</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>80</v>
@@ -13696,7 +13700,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13714,7 +13718,7 @@
         <v>80</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>319</v>
@@ -13731,10 +13735,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13760,13 +13764,13 @@
         <v>233</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O97" t="s" s="2">
         <v>326</v>
@@ -13797,10 +13801,10 @@
         <v>336</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>80</v>
@@ -13818,7 +13822,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13853,10 +13857,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13940,7 +13944,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13975,10 +13979,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14004,10 +14008,10 @@
         <v>81</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>393</v>
@@ -14062,7 +14066,7 @@
         <v>80</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14097,13 +14101,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>80</v>
@@ -14128,16 +14132,16 @@
         <v>390</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>80</v>
@@ -14186,7 +14190,7 @@
         <v>80</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14207,10 +14211,10 @@
         <v>80</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>80</v>
@@ -14221,10 +14225,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14339,10 +14343,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14455,13 +14459,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>80</v>
@@ -14483,13 +14487,13 @@
         <v>80</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14575,10 +14579,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14697,10 +14701,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14726,13 +14730,13 @@
         <v>233</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O105" t="s" s="2">
         <v>247</v>
@@ -14742,7 +14746,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>80</v>
@@ -14782,7 +14786,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>91</v>
@@ -14800,7 +14804,7 @@
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>252</v>
@@ -14817,10 +14821,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14843,16 +14847,16 @@
         <v>92</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>314</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O106" t="s" s="2">
         <v>316</v>
@@ -14865,7 +14869,7 @@
         <v>80</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>80</v>
@@ -14904,7 +14908,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14922,7 +14926,7 @@
         <v>80</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>319</v>
@@ -14939,10 +14943,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14968,13 +14972,13 @@
         <v>233</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O107" t="s" s="2">
         <v>326</v>
@@ -15005,10 +15009,10 @@
         <v>336</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>80</v>
@@ -15026,7 +15030,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15061,10 +15065,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15148,7 +15152,7 @@
         <v>80</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15183,10 +15187,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15212,10 +15216,10 @@
         <v>81</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>393</v>
@@ -15270,7 +15274,7 @@
         <v>80</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>

--- a/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
+++ b/fhir/StructureDefinition-ehealth-observation-wound-dimensions.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
